--- a/reports/spark/2026-07/spark_settlement_july_2026.xlsx
+++ b/reports/spark/2026-07/spark_settlement_july_2026.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Venues" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Sky Revenue" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Sky Direct" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Debt" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Venues" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sky Revenue" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sky Direct" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Debt" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>8602620.664871853</v>
+        <v>8637841.797098733</v>
       </c>
     </row>
     <row r="5">
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>131173.458458512</v>
+        <v>131355.6683177533</v>
       </c>
     </row>
     <row r="6">
@@ -517,7 +517,7 @@
     <row r="7">
       <c r="A7" t="inlineStr"/>
       <c r="B7" s="4" t="n">
-        <v>9677204.043330366</v>
+        <v>9712607.385416487</v>
       </c>
     </row>
     <row r="9">
@@ -539,7 +539,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>5755899.021376387</v>
+        <v>5799604.264476568</v>
       </c>
     </row>
     <row r="11">
@@ -555,7 +555,7 @@
     <row r="12">
       <c r="A12" t="inlineStr"/>
       <c r="B12" s="4" t="n">
-        <v>5750694.262689384</v>
+        <v>5794399.505789564</v>
       </c>
     </row>
     <row r="14">
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>5755899.021376387</v>
+        <v>5799604.264476568</v>
       </c>
     </row>
     <row r="16">
@@ -587,13 +587,13 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-3043688.233580878</v>
+        <v>-3047975.079849198</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr"/>
       <c r="B17" s="4" t="n">
-        <v>8799587.254957264</v>
+        <v>8847579.344325766</v>
       </c>
     </row>
     <row r="19">
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>82524.78406415794</v>
+        <v>82641.9247097662</v>
       </c>
     </row>
     <row r="21">
@@ -625,7 +625,7 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>8602620.664871853</v>
+        <v>8637841.797098733</v>
       </c>
     </row>
     <row r="23">
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>-5755899.021376387</v>
+        <v>-5799604.264476568</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
       <c r="B24" s="4" t="n">
-        <v>2652602.192543479</v>
+        <v>2644000.941024571</v>
       </c>
     </row>
     <row r="26">
@@ -676,7 +676,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-04T09:09:30+00:00</t>
+          <t>2026-09-01T17:41:24+00:00</t>
         </is>
       </c>
     </row>
@@ -703,7 +703,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S65"/>
+  <dimension ref="A1:S67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -855,13 +855,13 @@
         <v>-603044919.431178</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>1296477.299642093</v>
+        <v>1296477.299642261</v>
       </c>
       <c r="I2" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>1296477.299642093</v>
+        <v>1296477.299642261</v>
       </c>
       <c r="K2" s="6" t="n">
         <v>0</v>
@@ -873,13 +873,13 @@
         <v>1</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>1561606.197166973</v>
+        <v>1563805.186269314</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>1561606.197166973</v>
+        <v>1563805.186269314</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>-265128.8975248803</v>
+        <v>-267327.8866270527</v>
       </c>
       <c r="Q2" s="6" t="n">
         <v>0</v>
@@ -938,13 +938,13 @@
         <v>1</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>1179448.554894363</v>
+        <v>1181109.405449189</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>1179448.554894363</v>
+        <v>1181109.405449189</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>469701.9561466368</v>
+        <v>468041.1055918105</v>
       </c>
       <c r="Q3" s="6" t="n">
         <v>0</v>
@@ -1003,13 +1003,13 @@
         <v>1</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>611437.7255944717</v>
+        <v>612298.726849322</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>611437.7255944717</v>
+        <v>612298.726849322</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>284696.6941019864</v>
+        <v>283835.6928471362</v>
       </c>
       <c r="Q4" s="6" t="n">
         <v>226280049.6100522</v>
@@ -1072,13 +1072,13 @@
         <v>1</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>532983.5078446149</v>
+        <v>533734.0331227576</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>532983.5078446149</v>
+        <v>533734.0331227576</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>1030538.362155385</v>
+        <v>1029787.836877242</v>
       </c>
       <c r="Q5" s="6" t="n">
         <v>0</v>
@@ -1137,13 +1137,13 @@
         <v>1</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>450641.9011189062</v>
+        <v>451276.4763603573</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>450641.9011189062</v>
+        <v>451276.4763603573</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>-450641.9011189062</v>
+        <v>-451276.4763603573</v>
       </c>
       <c r="Q6" s="6" t="n">
         <v>0</v>
@@ -1202,13 +1202,13 @@
         <v>1</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>392202.5881209504</v>
+        <v>392754.8715447437</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>392202.5881209504</v>
+        <v>392754.8715447437</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>135615.0979709042</v>
+        <v>135062.814547111</v>
       </c>
       <c r="Q7" s="6" t="n">
         <v>97513234.98023258</v>
@@ -1271,19 +1271,19 @@
         <v>1</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>325303.2724624738</v>
+        <v>325761.351043616</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>292167.4059112128</v>
+        <v>292579.4806568798</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>105876.0690890528</v>
+        <v>105417.9905079107</v>
       </c>
       <c r="Q8" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R8" s="6" t="n">
-        <v>33135.86655126106</v>
+        <v>33181.8703867361</v>
       </c>
       <c r="S8" t="inlineStr"/>
     </row>
@@ -1336,13 +1336,13 @@
         <v>1</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>225618.246264197</v>
+        <v>225935.952524408</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>225618.246264197</v>
+        <v>225935.952524408</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>-202255.3116051969</v>
+        <v>-202573.017865408</v>
       </c>
       <c r="Q9" s="6" t="n">
         <v>0</v>
@@ -1401,19 +1401,19 @@
         <v>1</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>227827.468298817</v>
+        <v>228148.2854939024</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>204415.9196904151</v>
+        <v>204704.0101144359</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>84247.78386269569</v>
+        <v>83926.96666761028</v>
       </c>
       <c r="Q10" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R10" s="6" t="n">
-        <v>23411.54860840191</v>
+        <v>23444.2753794665</v>
       </c>
       <c r="S10" t="inlineStr"/>
     </row>
@@ -1448,31 +1448,31 @@
         <v>-105302337.3270564</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>223540.2679211392</v>
+        <v>223540.2679211321</v>
       </c>
       <c r="I11" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>223540.2679211392</v>
+        <v>223540.2679211321</v>
       </c>
       <c r="K11" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>51601571.63582894</v>
+        <v>51601571.63582895</v>
       </c>
       <c r="M11" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>116422.4998757615</v>
+        <v>116586.4412131862</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>116422.4998757615</v>
+        <v>116586.4412131862</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>107117.7680453776</v>
+        <v>106953.8267079459</v>
       </c>
       <c r="Q11" s="6" t="n">
         <v>0</v>
@@ -1531,19 +1531,19 @@
         <v>1</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>76712.53963857236</v>
+        <v>76820.56305637397</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>68035.95271877198</v>
+        <v>68131.00341104389</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>46253.16400095824</v>
+        <v>46145.14058315663</v>
       </c>
       <c r="Q12" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R12" s="6" t="n">
-        <v>8676.586919800378</v>
+        <v>8689.559645330075</v>
       </c>
       <c r="S12" t="inlineStr"/>
     </row>
@@ -1596,19 +1596,19 @@
         <v>1</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>72957.39746933564</v>
+        <v>73060.13305162349</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>64705.53664491809</v>
+        <v>64795.93452730458</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>43989.03342437145</v>
+        <v>43886.29784208361</v>
       </c>
       <c r="Q13" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R13" s="6" t="n">
-        <v>8251.860824417559</v>
+        <v>8264.198524318903</v>
       </c>
       <c r="S13" t="inlineStr"/>
     </row>
@@ -1661,13 +1661,13 @@
         <v>1</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>45388.16894073053</v>
+        <v>45452.08267843019</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>45388.16894073053</v>
+        <v>45452.08267843019</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>56523.41675837247</v>
+        <v>56459.50302067281</v>
       </c>
       <c r="Q14" s="6" t="n">
         <v>0</v>
@@ -1680,12 +1680,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S65</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Spark USDC (SparkLend spToken)</t>
+          <t>Spark Blue Chip USDT Vault (Morpho — 2026-06 redeployment)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1695,44 +1695,44 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E15" s="6" t="n">
-        <v>6740456.351987</v>
+        <v>45918530.85783745</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>11026528.088879</v>
+        <v>60823719.84933824</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>4286071.736892</v>
+        <v>14905188.99150079</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>20590.310642</v>
+        <v>35221.13222675498</v>
       </c>
       <c r="I15" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>20590.310642</v>
+        <v>35221.13222675498</v>
       </c>
       <c r="K15" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>6878052.527027323</v>
+        <v>15757109.7868005</v>
       </c>
       <c r="M15" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>15518.1333453286</v>
+        <v>35600.95740520028</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>15518.1333453286</v>
+        <v>35600.95740520028</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>5072.177296671395</v>
+        <v>-379.8251784453008</v>
       </c>
       <c r="Q15" s="6" t="n">
         <v>0</v>
@@ -1745,138 +1745,138 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SPREAD</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>30bps sUSDS spread (Curve LP + PSM3) — Sky Revenue reduction</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
+          <t>Spark USDC (SparkLend spToken)</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="E16" s="6" t="n">
-        <v>0</v>
+        <v>6740456.351987</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>0</v>
+        <v>11026528.088879</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0</v>
+        <v>4286071.736892</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0</v>
+        <v>20590.310642</v>
       </c>
       <c r="I16" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>0</v>
+        <v>20590.310642</v>
       </c>
       <c r="K16" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>0</v>
+        <v>6878052.527027323</v>
       </c>
       <c r="M16" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0</v>
+        <v>15539.98533732054</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>-9048.921160277027</v>
+        <v>15539.98533732054</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0</v>
+        <v>5050.325304679455</v>
       </c>
       <c r="Q16" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R16" s="6" t="n">
-        <v>9048.921160277027</v>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>sky-revenue reduction (no CoF; computed outside venue loop)</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="S16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S10</t>
+          <t>SPREAD</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Spark Blue Chip USDC Vault (Morpho)</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>ethereum</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
+          <t>30bps sUSDS spread (Curve LP + PSM3) — Sky Revenue reduction</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" s="6" t="n">
-        <v>640616.8200220506</v>
+        <v>0</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>772030.6797926712</v>
+        <v>0</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>131413.8597706206</v>
+        <v>0</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>6293.345125151918</v>
+        <v>0</v>
       </c>
       <c r="I17" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>6293.345125151918</v>
+        <v>0</v>
       </c>
       <c r="K17" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>1928994.071562365</v>
+        <v>0</v>
       </c>
       <c r="M17" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>4352.160310963879</v>
+        <v>0</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>4352.160310963879</v>
+        <v>-9062.020773914626</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>1941.184814188039</v>
+        <v>0</v>
       </c>
       <c r="Q17" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R17" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="inlineStr"/>
+        <v>9062.020773914626</v>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>sky-revenue reduction (no CoF; computed outside venue loop)</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S62</t>
+          <t>S10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Spark.fi USDT Reserve Uniswap V4 (USDT/USDS)</t>
+          <t>Spark Blue Chip USDC Vault (Morpho)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1886,66 +1886,62 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E18" s="6" t="n">
-        <v>50000000.01256605</v>
+        <v>640616.8200220506</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>50000939.1994665</v>
+        <v>772030.6797926712</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>939.1869004437085</v>
+        <v>131413.8597706206</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>-4037.82810665977</v>
+        <v>6293.345125150679</v>
       </c>
       <c r="I18" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>0</v>
+        <v>6293.345125150679</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>-4037.82810665977</v>
+        <v>0</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>50006045.38978972</v>
+        <v>1928994.071562365</v>
       </c>
       <c r="M18" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>0</v>
+        <v>4358.288842672331</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>-4037.82810665977</v>
+        <v>4358.288842672331</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>0</v>
+        <v>1935.056282478349</v>
       </c>
       <c r="Q18" s="6" t="n">
-        <v>50006045.38978972</v>
+        <v>0</v>
       </c>
       <c r="R18" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>SDE (fixed)</t>
-        </is>
-      </c>
+      <c r="S18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S61</t>
+          <t>S62</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Spark.fi PYUSD Reserve Uniswap V4 (PYUSD/USDS)</t>
+          <t>Spark.fi USDT Reserve Uniswap V4 (USDT/USDS)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1959,16 +1955,16 @@
         </is>
       </c>
       <c r="E19" s="6" t="n">
-        <v>100119969.930802</v>
+        <v>50000000.01256605</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>100118990.9295999</v>
+        <v>50000939.1994665</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>-979.0012021481182</v>
+        <v>939.1869004437085</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>-1166.931672093194</v>
+        <v>-4037.82810665977</v>
       </c>
       <c r="I19" s="6" t="n">
         <v>0</v>
@@ -1977,10 +1973,10 @@
         <v>0</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>-1166.931672093194</v>
+        <v>-4037.82810665977</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>100120066.3092816</v>
+        <v>50006045.38978972</v>
       </c>
       <c r="M19" s="7" t="n">
         <v>0</v>
@@ -1989,13 +1985,13 @@
         <v>0</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>-1166.931672093194</v>
+        <v>-4037.82810665977</v>
       </c>
       <c r="P19" s="6" t="n">
         <v>0</v>
       </c>
       <c r="Q19" s="6" t="n">
-        <v>100120066.3092816</v>
+        <v>50006045.38978972</v>
       </c>
       <c r="R19" s="6" t="n">
         <v>0</v>
@@ -2009,12 +2005,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>S61</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Spark DAI Vault (Morpho)</t>
+          <t>Spark.fi PYUSD Reserve Uniswap V4 (PYUSD/USDS)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2024,67 +2020,71 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E20" s="6" t="n">
-        <v>637.4866706248019</v>
+        <v>100119969.930802</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>725.7224774532416</v>
+        <v>100118990.9295999</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>88.23580682843965</v>
+        <v>-979.0012021481182</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>88.23580682843965</v>
+        <v>-1166.931672093194</v>
       </c>
       <c r="I20" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>88.23580682843965</v>
+        <v>0</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>0</v>
+        <v>-1166.931672093194</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>637.4866706248019</v>
+        <v>100120066.3092816</v>
       </c>
       <c r="M20" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>1.438285491678385</v>
+        <v>0</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>1.438285491678385</v>
+        <v>-1166.931672093194</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>86.79752133676126</v>
+        <v>0</v>
       </c>
       <c r="Q20" s="6" t="n">
-        <v>0</v>
+        <v>100120066.3092816</v>
       </c>
       <c r="R20" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S20" t="inlineStr"/>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>SDE (fixed)</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S34</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Spark USDC Vault (Morpho, Base)</t>
+          <t>Spark DAI Vault (Morpho)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2093,40 +2093,40 @@
         </is>
       </c>
       <c r="E21" s="6" t="n">
-        <v>394.3129623374141</v>
+        <v>637.4866706248019</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>193.3730438832657</v>
+        <v>725.7224774532416</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>-200.9399184541484</v>
+        <v>88.23580682843965</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>1.413937993106596</v>
+        <v>88.23580682843965</v>
       </c>
       <c r="I21" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>1.413937993106596</v>
+        <v>88.23580682843965</v>
       </c>
       <c r="K21" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>427.1489085815464</v>
+        <v>637.4866706248019</v>
       </c>
       <c r="M21" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>0.9637253707547445</v>
+        <v>1.440310825676159</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>0.9637253707547445</v>
+        <v>1.440310825676159</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>0.450212622351851</v>
+        <v>86.79549600276349</v>
       </c>
       <c r="Q21" s="6" t="n">
         <v>0</v>
@@ -2139,12 +2139,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S36</t>
+          <t>S34</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Fluid Savings USDS (fsUSDS, Base)</t>
+          <t>Spark USDC Vault (Morpho, Base)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2158,40 +2158,40 @@
         </is>
       </c>
       <c r="E22" s="6" t="n">
-        <v>283.8972488542868</v>
+        <v>394.3129623374141</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>283.8972488542868</v>
+        <v>193.3730438832657</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>0</v>
+        <v>-200.9399184541484</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>0</v>
+        <v>1.41393799010658</v>
       </c>
       <c r="I22" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0</v>
+        <v>1.41393799010658</v>
       </c>
       <c r="K22" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>283.8972488542868</v>
+        <v>427.1489085818044</v>
       </c>
       <c r="M22" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>0.6405236579367665</v>
+        <v>0.9650824488661753</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>0.6405236579367665</v>
+        <v>0.9650824488661753</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>-0.6405236579367665</v>
+        <v>0.4488555412404045</v>
       </c>
       <c r="Q22" s="6" t="n">
         <v>0</v>
@@ -2204,17 +2204,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>S16</t>
+          <t>S36</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Ethena Staked USDe (sUSDe)</t>
+          <t>Fluid Savings USDS (fsUSDS, Base)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2223,40 +2223,40 @@
         </is>
       </c>
       <c r="E23" s="6" t="n">
-        <v>100.1238263246728</v>
+        <v>283.8972488542868</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>100.4548689419015</v>
+        <v>283.8972488542868</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>0.3310426172286373</v>
+        <v>0</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>0.3310426172286373</v>
+        <v>0</v>
       </c>
       <c r="I23" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>0.3310426172286373</v>
+        <v>0</v>
       </c>
       <c r="K23" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L23" s="6" t="n">
-        <v>100.1238263246728</v>
+        <v>283.8972488542868</v>
       </c>
       <c r="M23" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0.2258975025045812</v>
+        <v>0.6414256167956325</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>0.2258975025045812</v>
+        <v>0.6414256167956325</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>0.105145114724056</v>
+        <v>-0.6414256167956325</v>
       </c>
       <c r="Q23" s="6" t="n">
         <v>0</v>
@@ -2269,59 +2269,59 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>S39</t>
+          <t>S16</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>USDC raw (Base — ALM idle)</t>
+          <t>Ethena Staked USDe (sUSDe)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E24" s="6" t="n">
-        <v>0</v>
+        <v>100.1238263246728</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>1326.975817</v>
+        <v>100.4548689419015</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>1326.975817</v>
+        <v>0.3310426172286373</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>0</v>
+        <v>0.3310426172286373</v>
       </c>
       <c r="I24" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>0</v>
+        <v>0.3310426172286373</v>
       </c>
       <c r="K24" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>42.80567151612903</v>
+        <v>100.1238263246728</v>
       </c>
       <c r="M24" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>0.09657735469646349</v>
+        <v>0.226215602001852</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>0.09657735469646349</v>
+        <v>0.226215602001852</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>-0.09657735469646349</v>
+        <v>0.1048270152267853</v>
       </c>
       <c r="Q24" s="6" t="n">
         <v>0</v>
@@ -2334,59 +2334,59 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>S13</t>
+          <t>S39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Spark USDS Vault (Morpho)</t>
+          <t>USDC raw (Base — ALM idle)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E25" s="6" t="n">
-        <v>21.90842102645718</v>
+        <v>0</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>21.94239521151591</v>
+        <v>1326.975817</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>0.03397418505873122</v>
+        <v>1326.975817</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>0.03397418505873122</v>
+        <v>0</v>
       </c>
       <c r="I25" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>0.03397418505873122</v>
+        <v>0</v>
       </c>
       <c r="K25" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>21.90842102645718</v>
+        <v>42.80567151612903</v>
       </c>
       <c r="M25" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>0.04942936936556096</v>
+        <v>0.09671335092323037</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>0.04942936936556096</v>
+        <v>0.09671335092323037</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>-0.01545518430682974</v>
+        <v>-0.09671335092323037</v>
       </c>
       <c r="Q25" s="6" t="n">
         <v>0</v>
@@ -2399,12 +2399,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>S9</t>
+          <t>S13</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Aave Ethereum USDT (aToken)</t>
+          <t>Spark USDS Vault (Morpho)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2414,44 +2414,44 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E26" s="6" t="n">
-        <v>5.924825</v>
+        <v>21.90842102645718</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>5.938459</v>
+        <v>21.94239521151591</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>0.013634</v>
+        <v>0.03397418505873122</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>0.013634</v>
+        <v>0.03397418505873122</v>
       </c>
       <c r="I26" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>0.013634</v>
+        <v>0.03397418505873122</v>
       </c>
       <c r="K26" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>5.924825</v>
+        <v>21.90842102645718</v>
       </c>
       <c r="M26" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>0.01336747924451716</v>
+        <v>0.04949897375414988</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>0.01336747924451716</v>
+        <v>0.04949897375414988</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>0.0002665207554828384</v>
+        <v>-0.01552478869541866</v>
       </c>
       <c r="Q26" s="6" t="n">
         <v>0</v>
@@ -2464,12 +2464,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>S25</t>
+          <t>S9</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Spark.fi PYUSD Reserve Curve (PYUSD/USDS)</t>
+          <t>Aave Ethereum USDT (aToken)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2479,44 +2479,44 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E27" s="6" t="n">
-        <v>3.882492536172616</v>
+        <v>5.924825</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>3.882540733930369</v>
+        <v>5.938459</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>4.819775775350545e-05</v>
+        <v>0.013634</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>4.819775775350545e-05</v>
+        <v>0.013634</v>
       </c>
       <c r="I27" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>4.819775775350545e-05</v>
+        <v>0.013634</v>
       </c>
       <c r="K27" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L27" s="6" t="n">
-        <v>3.882492536172616</v>
+        <v>5.924825</v>
       </c>
       <c r="M27" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>0.008759606974768071</v>
+        <v>0.01338630277457089</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>0.008759606974768071</v>
+        <v>0.01338630277457089</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>-0.008711409217014566</v>
+        <v>0.0002476972254291061</v>
       </c>
       <c r="Q27" s="6" t="n">
         <v>0</v>
@@ -2529,12 +2529,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>S11</t>
+          <t>S25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Spark Blue Chip USDT Vault (Morpho V2)</t>
+          <t>Spark.fi PYUSD Reserve Curve (PYUSD/USDS)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2544,44 +2544,44 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E28" s="6" t="n">
-        <v>1.753936570309431</v>
+        <v>3.882492536172616</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>1.75807157545523</v>
+        <v>3.882540733930369</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>0.004135005145799616</v>
+        <v>4.819775775350545e-05</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>0.004135005145799616</v>
+        <v>4.819775775350545e-05</v>
       </c>
       <c r="I28" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J28" s="6" t="n">
-        <v>0.004135005145799616</v>
+        <v>4.819775775350545e-05</v>
       </c>
       <c r="K28" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L28" s="6" t="n">
-        <v>1.753936570309431</v>
+        <v>3.882492536172616</v>
       </c>
       <c r="M28" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>0.003957198853942678</v>
+        <v>0.00877194189013486</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>0.003957198853942678</v>
+        <v>0.00877194189013486</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.0001778062918569384</v>
+        <v>-0.008723744132381354</v>
       </c>
       <c r="Q28" s="6" t="n">
         <v>0</v>
@@ -2594,12 +2594,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>S23</t>
+          <t>S11</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Anchorage tri-party loan escrow (USDC pass-through, ~$0 balance)</t>
+          <t>Spark Blue Chip USDT Vault (Morpho — pre-2026-06 deployment)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2609,44 +2609,44 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E29" s="6" t="n">
-        <v>1.353383</v>
+        <v>1.753936570309431</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>1.359103</v>
+        <v>1.75807157545523</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>0.00572</v>
+        <v>0.004135005145799616</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>0.00572</v>
+        <v>0.004135005145799616</v>
       </c>
       <c r="I29" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>0.00572</v>
+        <v>0.004135005145799616</v>
       </c>
       <c r="K29" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>1.353383</v>
+        <v>1.753936570309431</v>
       </c>
       <c r="M29" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>0.003053477387497921</v>
+        <v>0.003962771217302534</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>0.003053477387497921</v>
+        <v>0.003962771217302534</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>0.002666522612502079</v>
+        <v>0.0001722339284970823</v>
       </c>
       <c r="Q29" s="6" t="n">
         <v>0</v>
@@ -2659,12 +2659,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>S24</t>
+          <t>S23</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Spark.fi USDT Reserve Curve (sUSDS/USDT)</t>
+          <t>Anchorage tri-party loan escrow (USDC pass-through, ~$0 balance)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2674,136 +2674,136 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E30" s="6" t="n">
-        <v>0.823120129440027</v>
+        <v>1.353383</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>0.8244687442276728</v>
+        <v>1.359103</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>0.001348614787645832</v>
+        <v>0.00572</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>0.00109174911014533</v>
+        <v>0.00572</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>0.0002568656775005022</v>
+        <v>0</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>0.0002568656775005022</v>
+        <v>0.00572</v>
       </c>
       <c r="K30" s="6" t="n">
-        <v>0.00109174911014533</v>
+        <v>0</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>0.823120129440027</v>
+        <v>1.353383</v>
       </c>
       <c r="M30" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>0</v>
+        <v>0.003057777167757205</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>0.00109174911014533</v>
+        <v>0.003057777167757205</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>0.0002568656775005022</v>
+        <v>0.002662222832242795</v>
       </c>
       <c r="Q30" s="6" t="n">
-        <v>0.823120129440027</v>
+        <v>0</v>
       </c>
       <c r="R30" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>SDE (fixed)</t>
-        </is>
-      </c>
+      <c r="S30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>S54</t>
+          <t>S24</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Aave Avalanche USDC (aAvaUSDC)</t>
+          <t>Spark.fi USDT Reserve Curve (sUSDS/USDT)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>avalanche_c</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E31" s="6" t="n">
-        <v>0.155607</v>
+        <v>0.823120129440027</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>0.156077</v>
+        <v>0.8244687442276728</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>0.00047</v>
+        <v>0.001348614787645832</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>0.00047</v>
+        <v>0.00109174911014533</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>0</v>
+        <v>0.0002568656775005022</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>0.00047</v>
+        <v>0.0002568656775005022</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>0</v>
+        <v>0.00109174911014533</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>0.155607</v>
+        <v>0.823120129440027</v>
       </c>
       <c r="M31" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>0.0003510776002331853</v>
+        <v>0</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>0.0003510776002331853</v>
+        <v>0.00109174911014533</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>0.0001189223997668147</v>
+        <v>0.0002568656775005022</v>
       </c>
       <c r="Q31" s="6" t="n">
-        <v>0</v>
+        <v>0.823120129440027</v>
       </c>
       <c r="R31" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S31" t="inlineStr"/>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>SDE (fixed)</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>S8</t>
+          <t>S54</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Aave Ethereum USDC (aToken)</t>
+          <t>Aave Avalanche USDC (aAvaUSDC)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>avalanche_c</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2812,40 +2812,40 @@
         </is>
       </c>
       <c r="E32" s="6" t="n">
-        <v>0.058128</v>
+        <v>0.155607</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>0.058302</v>
+        <v>0.156077</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>0.000174</v>
+        <v>0.00047</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>0.000174</v>
+        <v>0.00047</v>
       </c>
       <c r="I32" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>0.000174</v>
+        <v>0.00047</v>
       </c>
       <c r="K32" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L32" s="6" t="n">
-        <v>0.058128</v>
+        <v>0.155607</v>
       </c>
       <c r="M32" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>0.0001311473053677186</v>
+        <v>0.0003515719731540852</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.0001311473053677186</v>
+        <v>0.0003515719731540852</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>4.285269463228136e-05</v>
+        <v>0.0001184280268459148</v>
       </c>
       <c r="Q32" s="6" t="n">
         <v>0</v>
@@ -2858,17 +2858,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>S41</t>
+          <t>S8</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Aave Arbitrum USDCn (aArbUSDCn)</t>
+          <t>Aave Ethereum USDC (aToken)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>arbitrum</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2877,40 +2877,40 @@
         </is>
       </c>
       <c r="E33" s="6" t="n">
-        <v>0.006375</v>
+        <v>0.058128</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>0.006389</v>
+        <v>0.058302</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>1.4e-05</v>
+        <v>0.000174</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>1.4e-05</v>
+        <v>0.000174</v>
       </c>
       <c r="I33" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J33" s="6" t="n">
-        <v>1.4e-05</v>
+        <v>0.000174</v>
       </c>
       <c r="K33" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L33" s="6" t="n">
-        <v>0.006375</v>
+        <v>0.058128</v>
       </c>
       <c r="M33" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>1.438315565165164e-05</v>
+        <v>0.0001313319815657436</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>1.438315565165164e-05</v>
+        <v>0.0001313319815657436</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>-3.831556516516362e-07</v>
+        <v>4.266801843425639e-05</v>
       </c>
       <c r="Q33" s="6" t="n">
         <v>0</v>
@@ -2923,17 +2923,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>S7</t>
+          <t>S41</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Aave Ethereum USDS (aToken)</t>
+          <t>Aave Arbitrum USDCn (aArbUSDCn)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>arbitrum</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2942,40 +2942,40 @@
         </is>
       </c>
       <c r="E34" s="6" t="n">
-        <v>0.005747618663969358</v>
+        <v>0.006375</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>0.005748588443741238</v>
+        <v>0.006389</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>9.697797718799999e-07</v>
+        <v>1.4e-05</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>9.697797718799999e-07</v>
+        <v>1.4e-05</v>
       </c>
       <c r="I34" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>9.697797718799999e-07</v>
+        <v>1.4e-05</v>
       </c>
       <c r="K34" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L34" s="6" t="n">
-        <v>0.005747618663969358</v>
+        <v>0.006375</v>
       </c>
       <c r="M34" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>1.29676696266995e-05</v>
+        <v>1.440340941511174e-05</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>1.29676696266995e-05</v>
+        <v>1.440340941511174e-05</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>-1.19978898548195e-05</v>
+        <v>-4.034094151117456e-07</v>
       </c>
       <c r="Q34" s="6" t="n">
         <v>0</v>
@@ -2988,17 +2988,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>S35</t>
+          <t>S7</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Aave Base USDC (aBasUSDC)</t>
+          <t>Aave Ethereum USDS (aToken)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -3007,40 +3007,40 @@
         </is>
       </c>
       <c r="E35" s="6" t="n">
-        <v>0.001709</v>
+        <v>0.005747618663969358</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>0.001714</v>
+        <v>0.005748588443741238</v>
       </c>
       <c r="G35" s="6" t="n">
-        <v>5e-06</v>
+        <v>9.697797718799999e-07</v>
       </c>
       <c r="H35" s="6" t="n">
-        <v>5e-06</v>
+        <v>9.697797718799999e-07</v>
       </c>
       <c r="I35" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J35" s="6" t="n">
-        <v>5e-06</v>
+        <v>9.697797718799999e-07</v>
       </c>
       <c r="K35" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L35" s="6" t="n">
-        <v>0.001709</v>
+        <v>0.005747618663969358</v>
       </c>
       <c r="M35" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N35" s="6" t="n">
-        <v>3.855813805281984e-06</v>
+        <v>1.298593016142561e-05</v>
       </c>
       <c r="O35" s="6" t="n">
-        <v>3.855813805281984e-06</v>
+        <v>1.298593016142561e-05</v>
       </c>
       <c r="P35" s="6" t="n">
-        <v>1.144186194718016e-06</v>
+        <v>-1.201615038954561e-05</v>
       </c>
       <c r="Q35" s="6" t="n">
         <v>0</v>
@@ -3053,59 +3053,59 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>S17</t>
+          <t>S35</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Fluid Savings USDS (fsUSDS)</t>
+          <t>Aave Base USDC (aBasUSDC)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E36" s="6" t="n">
-        <v>0.001240144670509943</v>
+        <v>0.001709</v>
       </c>
       <c r="F36" s="6" t="n">
-        <v>0.001240144670509943</v>
+        <v>0.001714</v>
       </c>
       <c r="G36" s="6" t="n">
-        <v>0</v>
+        <v>5e-06</v>
       </c>
       <c r="H36" s="6" t="n">
-        <v>0</v>
+        <v>5e-06</v>
       </c>
       <c r="I36" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J36" s="6" t="n">
-        <v>0</v>
+        <v>5e-06</v>
       </c>
       <c r="K36" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L36" s="6" t="n">
-        <v>0.001240144670509943</v>
+        <v>0.001709</v>
       </c>
       <c r="M36" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N36" s="6" t="n">
-        <v>2.797991188472274e-06</v>
+        <v>3.861243402419761e-06</v>
       </c>
       <c r="O36" s="6" t="n">
-        <v>2.797991188472274e-06</v>
+        <v>3.861243402419761e-06</v>
       </c>
       <c r="P36" s="6" t="n">
-        <v>-2.797991188472274e-06</v>
+        <v>1.138756597580239e-06</v>
       </c>
       <c r="Q36" s="6" t="n">
         <v>0</v>
@@ -3118,12 +3118,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>S6</t>
+          <t>S17</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Aave Ethereum Lido USDS (aToken)</t>
+          <t>Fluid Savings USDS (fsUSDS)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -3133,44 +3133,44 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E37" s="6" t="n">
-        <v>0.000522139801452544</v>
+        <v>0.001240144670509943</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>0.000522446400962938</v>
+        <v>0.001240144670509943</v>
       </c>
       <c r="G37" s="6" t="n">
-        <v>3.06599510394e-07</v>
+        <v>0</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>3.06599510394e-07</v>
+        <v>0</v>
       </c>
       <c r="I37" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J37" s="6" t="n">
-        <v>3.06599510394e-07</v>
+        <v>0</v>
       </c>
       <c r="K37" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L37" s="6" t="n">
-        <v>0.000522139801452544</v>
+        <v>0.001240144670509943</v>
       </c>
       <c r="M37" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>1.17804204489638e-06</v>
+        <v>2.801931203658599e-06</v>
       </c>
       <c r="O37" s="6" t="n">
-        <v>1.17804204489638e-06</v>
+        <v>2.801931203658599e-06</v>
       </c>
       <c r="P37" s="6" t="n">
-        <v>-8.714425345023799e-07</v>
+        <v>-2.801931203658599e-06</v>
       </c>
       <c r="Q37" s="6" t="n">
         <v>0</v>
@@ -3183,12 +3183,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>S30</t>
+          <t>S6</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>USDe raw (ALM idle)</t>
+          <t>Aave Ethereum Lido USDS (aToken)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -3198,44 +3198,44 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E38" s="6" t="n">
-        <v>7.4896275897803e-05</v>
+        <v>0.000522139801452544</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>7.4896275897803e-05</v>
+        <v>0.000522446400962938</v>
       </c>
       <c r="G38" s="6" t="n">
-        <v>0</v>
+        <v>3.06599510394e-07</v>
       </c>
       <c r="H38" s="6" t="n">
-        <v>0</v>
+        <v>3.06599510394e-07</v>
       </c>
       <c r="I38" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J38" s="6" t="n">
-        <v>0</v>
+        <v>3.06599510394e-07</v>
       </c>
       <c r="K38" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L38" s="6" t="n">
-        <v>7.4896275897803e-05</v>
+        <v>0.000522139801452544</v>
       </c>
       <c r="M38" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N38" s="6" t="n">
-        <v>1.689795755242581e-07</v>
+        <v>1.179700914862141e-06</v>
       </c>
       <c r="O38" s="6" t="n">
-        <v>1.689795755242581e-07</v>
+        <v>1.179700914862141e-06</v>
       </c>
       <c r="P38" s="6" t="n">
-        <v>-1.689795755242581e-07</v>
+        <v>-8.731014044681411e-07</v>
       </c>
       <c r="Q38" s="6" t="n">
         <v>0</v>
@@ -3248,12 +3248,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>S15</t>
+          <t>S30</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Maple syrupUSDT (ERC-4626)</t>
+          <t>USDe raw (ALM idle)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3263,14 +3263,14 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E39" s="6" t="n">
-        <v>0</v>
+        <v>7.4896275897803e-05</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>0</v>
+        <v>7.4896275897803e-05</v>
       </c>
       <c r="G39" s="6" t="n">
         <v>0</v>
@@ -3288,19 +3288,19 @@
         <v>0</v>
       </c>
       <c r="L39" s="6" t="n">
-        <v>0</v>
+        <v>7.4896275897803e-05</v>
       </c>
       <c r="M39" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>0</v>
+        <v>1.692175255565839e-07</v>
       </c>
       <c r="O39" s="6" t="n">
-        <v>0</v>
+        <v>1.692175255565839e-07</v>
       </c>
       <c r="P39" s="6" t="n">
-        <v>0</v>
+        <v>-1.692175255565839e-07</v>
       </c>
       <c r="Q39" s="6" t="n">
         <v>0</v>
@@ -3313,12 +3313,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>S19</t>
+          <t>S15</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>BlackRock USD Institutional Digital Liquidity Fund (BUIDL-I)</t>
+          <t>Maple syrupUSDT (ERC-4626)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3328,7 +3328,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E40" s="6" t="n">
@@ -3378,12 +3378,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>S20</t>
+          <t>S19</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Janus Henderson Anemoy Treasury Fund (JTRSY)</t>
+          <t>BlackRock USD Institutional Digital Liquidity Fund (BUIDL-I)</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3443,12 +3443,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>S21</t>
+          <t>S20</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Superstate Short Duration US Government Securities Fund (USTB)</t>
+          <t>Janus Henderson Anemoy Treasury Fund (JTRSY)</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3486,7 +3486,7 @@
         <v>0</v>
       </c>
       <c r="M42" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N42" s="6" t="n">
         <v>0</v>
@@ -3503,21 +3503,17 @@
       <c r="R42" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S42" t="inlineStr">
-        <is>
-          <t>SDE (fixed)</t>
-        </is>
-      </c>
+      <c r="S42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>S22</t>
+          <t>S21</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Superstate Crypto Carry Fund (USCC)</t>
+          <t>Superstate Short Duration US Government Securities Fund (USTB)</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3555,7 +3551,7 @@
         <v>0</v>
       </c>
       <c r="M43" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N43" s="6" t="n">
         <v>0</v>
@@ -3572,17 +3568,21 @@
       <c r="R43" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S43" t="inlineStr"/>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>SDE (fixed)</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>S26</t>
+          <t>S22</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>USDC raw (ALM idle)</t>
+          <t>Superstate Crypto Carry Fund (USCC)</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3592,7 +3592,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E44" s="6" t="n">
@@ -3605,13 +3605,13 @@
         <v>0</v>
       </c>
       <c r="H44" s="6" t="n">
-        <v>1198968.999999979</v>
+        <v>0</v>
       </c>
       <c r="I44" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J44" s="6" t="n">
-        <v>1198968.999999979</v>
+        <v>0</v>
       </c>
       <c r="K44" s="6" t="n">
         <v>0</v>
@@ -3629,7 +3629,7 @@
         <v>0</v>
       </c>
       <c r="P44" s="6" t="n">
-        <v>1198968.999999979</v>
+        <v>0</v>
       </c>
       <c r="Q44" s="6" t="n">
         <v>0</v>
@@ -3642,12 +3642,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>S29</t>
+          <t>S26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>DAI raw (ALM idle)</t>
+          <t>USDC raw (ALM idle)</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3670,13 +3670,13 @@
         <v>0</v>
       </c>
       <c r="H45" s="6" t="n">
-        <v>0</v>
+        <v>1198968.999999947</v>
       </c>
       <c r="I45" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J45" s="6" t="n">
-        <v>0</v>
+        <v>1198968.999999947</v>
       </c>
       <c r="K45" s="6" t="n">
         <v>0</v>
@@ -3694,7 +3694,7 @@
         <v>0</v>
       </c>
       <c r="P45" s="6" t="n">
-        <v>0</v>
+        <v>1198968.999999947</v>
       </c>
       <c r="Q45" s="6" t="n">
         <v>0</v>
@@ -3707,12 +3707,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>S31</t>
+          <t>S64</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>USDS raw / POL (ALM idle — already netted out of utilized)</t>
+          <t>RLUSD raw (ALM idle — $251.7M as of 2026-08)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3750,7 +3750,7 @@
         <v>0</v>
       </c>
       <c r="M46" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N46" s="6" t="n">
         <v>0</v>
@@ -3767,26 +3767,22 @@
       <c r="R46" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S46" t="inlineStr">
-        <is>
-          <t>CoF excluded (already deducted from utilized)</t>
-        </is>
-      </c>
+      <c r="S46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>S38</t>
+          <t>S29</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>USDS raw (Base — POL)</t>
+          <t>DAI raw (ALM idle)</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3795,13 +3791,13 @@
         </is>
       </c>
       <c r="E47" s="6" t="n">
-        <v>146550618.2104181</v>
+        <v>0</v>
       </c>
       <c r="F47" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G47" s="6" t="n">
-        <v>-146550618.2104181</v>
+        <v>0</v>
       </c>
       <c r="H47" s="6" t="n">
         <v>0</v>
@@ -3816,10 +3812,10 @@
         <v>0</v>
       </c>
       <c r="L47" s="6" t="n">
-        <v>141823178.9133078</v>
+        <v>0</v>
       </c>
       <c r="M47" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N47" s="6" t="n">
         <v>0</v>
@@ -3831,36 +3827,32 @@
         <v>0</v>
       </c>
       <c r="Q47" s="6" t="n">
-        <v>141823178.9133078</v>
+        <v>0</v>
       </c>
       <c r="R47" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S47" t="inlineStr">
-        <is>
-          <t>CoF excluded (already deducted from utilized)</t>
-        </is>
-      </c>
+      <c r="S47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>S42</t>
+          <t>S31</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Fluid Savings USDS (fsUSDS, Arbitrum)</t>
+          <t>USDS raw / POL (ALM idle — already netted out of utilized)</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>arbitrum</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E48" s="6" t="n">
@@ -3888,7 +3880,7 @@
         <v>0</v>
       </c>
       <c r="M48" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N48" s="6" t="n">
         <v>0</v>
@@ -3905,22 +3897,26 @@
       <c r="R48" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S48" t="inlineStr"/>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>CoF excluded (already deducted from utilized)</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>S44</t>
+          <t>S38</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>USDS raw (Arbitrum — POL)</t>
+          <t>USDS raw (Base — POL)</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>arbitrum</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3929,13 +3925,13 @@
         </is>
       </c>
       <c r="E49" s="6" t="n">
-        <v>90000000</v>
+        <v>146550618.2104181</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>90000000</v>
+        <v>0</v>
       </c>
       <c r="G49" s="6" t="n">
-        <v>0</v>
+        <v>-146550618.2104181</v>
       </c>
       <c r="H49" s="6" t="n">
         <v>0</v>
@@ -3950,7 +3946,7 @@
         <v>0</v>
       </c>
       <c r="L49" s="6" t="n">
-        <v>90000000</v>
+        <v>141823178.9133078</v>
       </c>
       <c r="M49" s="7" t="n">
         <v>0</v>
@@ -3965,7 +3961,7 @@
         <v>0</v>
       </c>
       <c r="Q49" s="6" t="n">
-        <v>90000000</v>
+        <v>141823178.9133078</v>
       </c>
       <c r="R49" s="6" t="n">
         <v>0</v>
@@ -3979,12 +3975,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>S45</t>
+          <t>S42</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>USDC raw (Arbitrum — ALM idle)</t>
+          <t>Fluid Savings USDS (fsUSDS, Arbitrum)</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3994,7 +3990,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E50" s="6" t="n">
@@ -4044,17 +4040,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>S48</t>
+          <t>S44</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>USDS raw (Optimism — POL)</t>
+          <t>USDS raw (Arbitrum — POL)</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>optimism</t>
+          <t>arbitrum</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -4063,13 +4059,13 @@
         </is>
       </c>
       <c r="E51" s="6" t="n">
-        <v>100304256.5863323</v>
+        <v>90000000</v>
       </c>
       <c r="F51" s="6" t="n">
-        <v>0</v>
+        <v>90000000</v>
       </c>
       <c r="G51" s="6" t="n">
-        <v>-100304256.5863323</v>
+        <v>0</v>
       </c>
       <c r="H51" s="6" t="n">
         <v>0</v>
@@ -4084,7 +4080,7 @@
         <v>0</v>
       </c>
       <c r="L51" s="6" t="n">
-        <v>97068635.40612808</v>
+        <v>90000000</v>
       </c>
       <c r="M51" s="7" t="n">
         <v>0</v>
@@ -4099,7 +4095,7 @@
         <v>0</v>
       </c>
       <c r="Q51" s="6" t="n">
-        <v>97068635.40612808</v>
+        <v>90000000</v>
       </c>
       <c r="R51" s="6" t="n">
         <v>0</v>
@@ -4113,17 +4109,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>S49</t>
+          <t>S45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>USDC raw (Optimism — ALM idle)</t>
+          <t>USDC raw (Arbitrum — ALM idle)</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>optimism</t>
+          <t>arbitrum</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -4178,17 +4174,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>S52</t>
+          <t>S48</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>USDS raw (Unichain — POL)</t>
+          <t>USDS raw (Optimism — POL)</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>unichain</t>
+          <t>optimism</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -4197,13 +4193,13 @@
         </is>
       </c>
       <c r="E53" s="6" t="n">
-        <v>99990828.81481861</v>
+        <v>100304256.5863323</v>
       </c>
       <c r="F53" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G53" s="6" t="n">
-        <v>-99990828.81481861</v>
+        <v>-100304256.5863323</v>
       </c>
       <c r="H53" s="6" t="n">
         <v>0</v>
@@ -4218,7 +4214,7 @@
         <v>0</v>
       </c>
       <c r="L53" s="6" t="n">
-        <v>96765318.20788898</v>
+        <v>97068635.40612808</v>
       </c>
       <c r="M53" s="7" t="n">
         <v>0</v>
@@ -4233,7 +4229,7 @@
         <v>0</v>
       </c>
       <c r="Q53" s="6" t="n">
-        <v>96765318.20788898</v>
+        <v>97068635.40612808</v>
       </c>
       <c r="R53" s="6" t="n">
         <v>0</v>
@@ -4247,17 +4243,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>S53</t>
+          <t>S49</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>USDC raw (Unichain — ALM idle)</t>
+          <t>USDC raw (Optimism — ALM idle)</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>unichain</t>
+          <t>optimism</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -4312,17 +4308,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>S55</t>
+          <t>S52</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>USDC raw (Avalanche-C — ALM idle)</t>
+          <t>USDS raw (Unichain — POL)</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>avalanche_c</t>
+          <t>unichain</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -4331,13 +4327,13 @@
         </is>
       </c>
       <c r="E55" s="6" t="n">
-        <v>0</v>
+        <v>99990828.81481861</v>
       </c>
       <c r="F55" s="6" t="n">
         <v>0</v>
       </c>
       <c r="G55" s="6" t="n">
-        <v>0</v>
+        <v>-99990828.81481861</v>
       </c>
       <c r="H55" s="6" t="n">
         <v>0</v>
@@ -4352,10 +4348,10 @@
         <v>0</v>
       </c>
       <c r="L55" s="6" t="n">
-        <v>0</v>
+        <v>96765318.20788898</v>
       </c>
       <c r="M55" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N55" s="6" t="n">
         <v>0</v>
@@ -4367,178 +4363,256 @@
         <v>0</v>
       </c>
       <c r="Q55" s="6" t="n">
-        <v>0</v>
+        <v>96765318.20788898</v>
       </c>
       <c r="R55" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S55" t="inlineStr"/>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>CoF excluded (already deducted from utilized)</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
+          <t>S53</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>USDC raw (Unichain — ALM idle)</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>unichain</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>S55</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>USDC raw (Avalanche-C — ALM idle)</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>avalanche_c</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E57" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N57" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O57" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P57" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q57" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R57" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
           <t>PSM_CURVE_DEDUCT</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B58" t="inlineStr">
         <is>
           <t>PSM3 USDS + PSM3 USDC (SDE) + Curve idle USDS — BR deduction (unattributed)</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr"/>
-      <c r="D56" t="inlineStr"/>
-      <c r="E56" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F56" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G56" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H56" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I56" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J56" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K56" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L56" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M56" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N56" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O56" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P56" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q56" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R56" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S56" t="inlineStr">
+      <c r="C58" t="inlineStr"/>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N58" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O58" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P58" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R58" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S58" t="inlineStr">
         <is>
           <t>BR deduction from PSM3 USDS leg + PSM3 USDC leg (SDE, ≈$0 yield) + Curve idle USDS — not tracked per-venue; residual = sky_rev_br_reduction − Σ(known venue deduction_avg × effective_br_rate × n_days)</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="8" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="8" t="inlineStr">
         <is>
           <t>Position-only venues (PnL aggregated at prime level)</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>Venue</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
         <is>
           <t>Label</t>
         </is>
       </c>
-      <c r="C59" s="2" t="inlineStr">
+      <c r="C61" s="2" t="inlineStr">
         <is>
           <t>Chain</t>
         </is>
       </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>Pricing cat.</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>Position SoM</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>Position EoM</t>
         </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>S56</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Spark Savings V2 — spUSDC vault</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>ethereum</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>S2</t>
-        </is>
-      </c>
-      <c r="E60" s="6" t="n">
-        <v>317193040.533521</v>
-      </c>
-      <c r="F60" s="6" t="n">
-        <v>268629480.765079</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>S57</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Spark Savings V2 — spUSDT vault</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>ethereum</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>S2</t>
-        </is>
-      </c>
-      <c r="E61" s="6" t="n">
-        <v>863439216.480082</v>
-      </c>
-      <c r="F61" s="6" t="n">
-        <v>404579096.135245</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>S59</t>
+          <t>S56</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Spark Savings V2 — spPYUSD vault</t>
+          <t>Spark Savings V2 — spUSDC vault</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -4552,26 +4626,26 @@
         </is>
       </c>
       <c r="E62" s="6" t="n">
-        <v>797030.383413</v>
+        <v>317193040.533521</v>
       </c>
       <c r="F62" s="6" t="n">
-        <v>30570.4865</v>
+        <v>268629480.765079</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>S60</t>
+          <t>S57</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Spark Savings V2 — spUSDC vault (Avalanche-C, CREATE2 same address)</t>
+          <t>Spark Savings V2 — spUSDT vault</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>avalanche_c</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -4580,51 +4654,107 @@
         </is>
       </c>
       <c r="E63" s="6" t="n">
-        <v>19103797.28946</v>
+        <v>863439216.480082</v>
       </c>
       <c r="F63" s="6" t="n">
-        <v>12460370.146586</v>
+        <v>404579096.135245</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
+          <t>S59</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Spark Savings V2 — spPYUSD vault</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="E64" s="6" t="n">
+        <v>797030.383413</v>
+      </c>
+      <c r="F64" s="6" t="n">
+        <v>30570.4865</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>S60</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Spark Savings V2 — spUSDC vault (Avalanche-C, CREATE2 same address)</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>avalanche_c</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="E65" s="6" t="n">
+        <v>19103797.28946</v>
+      </c>
+      <c r="F65" s="6" t="n">
+        <v>12460370.146586</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
           <t>S63</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
+      <c r="B66" t="inlineStr">
         <is>
           <t>Spark Savings V2 — spUSDG vault (Robinhood Chain)</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
+      <c r="C66" t="inlineStr">
         <is>
           <t>robinhood</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
+      <c r="D66" t="inlineStr">
         <is>
           <t>S2</t>
         </is>
       </c>
-      <c r="E64" s="6" t="n">
+      <c r="E66" s="6" t="n">
         <v>440606.057822</v>
       </c>
-      <c r="F64" s="6" t="n">
+      <c r="F66" s="6" t="n">
         <v>21723212.723921</v>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" t="inlineStr"/>
-      <c r="B65" s="5" t="inlineStr">
+    <row r="67">
+      <c r="A67" t="inlineStr"/>
+      <c r="B67" s="5" t="inlineStr">
         <is>
           <t>Aggregated actual_revenue (included in prime_agent_revenue, not in Venues body above)</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr"/>
-      <c r="D65" t="inlineStr"/>
-      <c r="E65" t="inlineStr"/>
-      <c r="F65" s="9" t="n">
+      <c r="C67" t="inlineStr"/>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4705,11 +4835,11 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Base rate (BR = SSR (+) spread; 30bps, 20bps from 2026-07-23), period avg</t>
+          <t>Base rate (BR_apr = apy_to_apr(SSR,12) + spread; 30bps, 20bps from 2026-07-23), period avg</t>
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>0.03867995992698061</v>
+        <v>0.0380059120516574</v>
       </c>
     </row>
     <row r="9">
@@ -4729,7 +4859,7 @@
         </is>
       </c>
       <c r="B10" s="7" t="n">
-        <v>0.03806862645474302</v>
+        <v>0.0378349784319679</v>
       </c>
     </row>
     <row r="11">
@@ -4739,7 +4869,7 @@
         </is>
       </c>
       <c r="B11" s="10" t="n">
-        <v>0.03840263381716146</v>
+        <v>0.03796803867319482</v>
       </c>
     </row>
     <row r="12">
@@ -4749,7 +4879,7 @@
         </is>
       </c>
       <c r="B12" s="11" t="n">
-        <v>-2.773261098191523</v>
+        <v>-0.3787337846257892</v>
       </c>
     </row>
     <row r="13">
@@ -4759,7 +4889,7 @@
         </is>
       </c>
       <c r="B13" s="12" t="n">
-        <v>41388.94518157523</v>
+        <v>5867.580836889359</v>
       </c>
     </row>
     <row r="15">
@@ -4769,7 +4899,7 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>5879812.750622121</v>
+        <v>5888113.770023223</v>
       </c>
     </row>
     <row r="16">
@@ -4779,7 +4909,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>5838423.805440546</v>
+        <v>5882246.189186334</v>
       </c>
     </row>
     <row r="17">
@@ -4789,7 +4919,7 @@
         </is>
       </c>
       <c r="B17" s="12" t="n">
-        <v>41388.94518157523</v>
+        <v>5867.580836889359</v>
       </c>
     </row>
     <row r="19">
@@ -4819,7 +4949,7 @@
         <v>1000000000</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>3173331.956622727</v>
+        <v>3213381.72983837</v>
       </c>
     </row>
     <row r="21">
@@ -4832,7 +4962,7 @@
         <v>824131757.9472046</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>2665091.848817819</v>
+        <v>2668864.459347963</v>
       </c>
     </row>
     <row r="23">
@@ -4854,7 +4984,7 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>5755899.021376387</v>
+        <v>5799604.264476568</v>
       </c>
     </row>
     <row r="25">
@@ -4874,7 +5004,7 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>5750694.262689384</v>
+        <v>5794399.505789564</v>
       </c>
     </row>
     <row r="28">
@@ -4891,7 +5021,7 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>8799587.254957264</v>
+        <v>8847579.344325766</v>
       </c>
     </row>
     <row r="31">
@@ -4901,7 +5031,7 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>5755899.021376387</v>
+        <v>5799604.264476568</v>
       </c>
     </row>
     <row r="32">
@@ -4911,7 +5041,7 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>-3043688.233580878</v>
+        <v>-3047975.079849198</v>
       </c>
     </row>
     <row r="33" ht="60" customHeight="1">
@@ -4928,7 +5058,7 @@
         </is>
       </c>
       <c r="B35" s="3" t="n">
-        <v>82524.78406415794</v>
+        <v>82641.9247097662</v>
       </c>
     </row>
     <row r="37">
@@ -5019,14 +5149,14 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>subsidised_apy = ref_rate + (base_apy − ref_rate) × min(T, 24) / 24, applied to first cap_usd of utilized; excess at full base_apy</t>
+          <t>subsidised_apr = ref_rate + (base_apr − ref_rate) × min(T, 24) / 24, applied to first cap_usd of utilized; excess at full base_apr</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>Base rate composition: base_apy = (1 + SSR)(1 + spread) − 1 (multiplicative; spread 30bps, 20bps from 2026-07-23)</t>
+          <t>Base rate composition: base_apr = apy_to_apr(SSR, n=12) + spread (nominal; spread 30bps, 20bps from 2026-07-23). Daily charge = utilized_d x base_apr / 365 — no intra-month compounding.</t>
         </is>
       </c>
     </row>
@@ -5324,7 +5454,7 @@
     <row r="3" ht="45" customHeight="1">
       <c r="A3" s="13" t="inlineStr">
         <is>
-          <t>cum_debt = Σ on-chain Vat dart from frob (0x76088703) + grab (0x7bab3f40), then scaled by Vat.ilks[ilk].rate_d / 1e27 read at each day's EoD block — actual outstanding USDS per day, not raw normalised Art. utilized = cum_debt − Σ deductions. base_apy = (1+SSR)(1+spread)−1 (multiplicative; spread 30bps, 20bps from 2026-07-23). sub_apy applies on the first cap_usd of utilized when the subsidy is active; excess pays base_apy.</t>
+          <t>cum_debt = Σ on-chain Vat dart from frob (0x76088703) + grab (0x7bab3f40), then scaled by Vat.ilks[ilk].rate_d / 1e27 read at each day's EoD block — actual outstanding USDS per day, not raw normalised Art. utilized = cum_debt − Σ deductions. base_apr = apy_to_apr(SSR, n=12) + spread (nominal; spread 30bps, 20bps from 2026-07-23). sub_apr applies on the first cap_usd of utilized when the subsidy is active; excess pays base_apr.</t>
         </is>
       </c>
     </row>
@@ -5375,7 +5505,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>base APY</t>
+          <t>base APR</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -5385,12 +5515,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>ref_rate APY</t>
+          <t>ref_rate APR</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>sub APY</t>
+          <t>sub APR</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5435,7 +5565,7 @@
         <v>0.03600000425292382</v>
       </c>
       <c r="J6" s="7" t="n">
-        <v>0.03910800426568259</v>
+        <v>0.03841931731351311</v>
       </c>
       <c r="K6" t="n">
         <v>6</v>
@@ -5444,13 +5574,13 @@
         <v>0.0385</v>
       </c>
       <c r="M6" s="7" t="n">
-        <v>0.03865200106642065</v>
+        <v>0.03841931731351311</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>285130.1666057298</v>
+        <v>286740.6953658817</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>378201.9984105768</v>
+        <v>379945.093016007</v>
       </c>
     </row>
     <row r="7">
@@ -5484,7 +5614,7 @@
         <v>0.03600000425292382</v>
       </c>
       <c r="J7" s="7" t="n">
-        <v>0.03910800426568259</v>
+        <v>0.03841931731351311</v>
       </c>
       <c r="K7" t="n">
         <v>6</v>
@@ -5493,13 +5623,13 @@
         <v>0.0382</v>
       </c>
       <c r="M7" s="7" t="n">
-        <v>0.03842700106642065</v>
+        <v>0.03825482932837828</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>257742.2422062334</v>
+        <v>259457.5790291576</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>350855.5484938333</v>
+        <v>352703.5102357614</v>
       </c>
     </row>
     <row r="8">
@@ -5533,7 +5663,7 @@
         <v>0.03600000425292382</v>
       </c>
       <c r="J8" s="7" t="n">
-        <v>0.03910800426568259</v>
+        <v>0.03841931731351311</v>
       </c>
       <c r="K8" t="n">
         <v>6</v>
@@ -5542,13 +5672,13 @@
         <v>0.0382</v>
       </c>
       <c r="M8" s="7" t="n">
-        <v>0.03842700106642065</v>
+        <v>0.03825482932837828</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>259221.2756786233</v>
+        <v>260938.7191466909</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>351358.6135244279</v>
+        <v>353207.2918015281</v>
       </c>
     </row>
     <row r="9">
@@ -5582,7 +5712,7 @@
         <v>0.03600000425292382</v>
       </c>
       <c r="J9" s="7" t="n">
-        <v>0.03910800426568259</v>
+        <v>0.03841931731351311</v>
       </c>
       <c r="K9" t="n">
         <v>6</v>
@@ -5591,13 +5721,13 @@
         <v>0.0382</v>
       </c>
       <c r="M9" s="7" t="n">
-        <v>0.03842700106642065</v>
+        <v>0.03825482932837828</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>257341.5718602723</v>
+        <v>259056.3379927731</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>349939.7908933141</v>
+        <v>351786.4482859237</v>
       </c>
     </row>
     <row r="10">
@@ -5631,7 +5761,7 @@
         <v>0.03600000425292382</v>
       </c>
       <c r="J10" s="7" t="n">
-        <v>0.03910800426568259</v>
+        <v>0.03841931731351311</v>
       </c>
       <c r="K10" t="n">
         <v>6</v>
@@ -5640,13 +5770,13 @@
         <v>0.0382</v>
       </c>
       <c r="M10" s="7" t="n">
-        <v>0.03842700106642065</v>
+        <v>0.03825482932837828</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>256953.6408377658</v>
+        <v>258667.8544249593</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>349500.8594088926</v>
+        <v>351346.8916142451</v>
       </c>
     </row>
     <row r="11">
@@ -5680,7 +5810,7 @@
         <v>0.03600000425292382</v>
       </c>
       <c r="J11" s="7" t="n">
-        <v>0.03910800426568259</v>
+        <v>0.03841931731351311</v>
       </c>
       <c r="K11" t="n">
         <v>6</v>
@@ -5689,13 +5819,13 @@
         <v>0.0387</v>
       </c>
       <c r="M11" s="7" t="n">
-        <v>0.03880200106642065</v>
+        <v>0.03841931731351311</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>258302.0859345911</v>
+        <v>259478.1605765379</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>351572.5239269125</v>
+        <v>352881.4472966876</v>
       </c>
     </row>
     <row r="12">
@@ -5729,7 +5859,7 @@
         <v>0.03600000425292382</v>
       </c>
       <c r="J12" s="7" t="n">
-        <v>0.03910800426568259</v>
+        <v>0.03841931731351311</v>
       </c>
       <c r="K12" t="n">
         <v>6</v>
@@ -5738,13 +5868,13 @@
         <v>0.0386</v>
       </c>
       <c r="M12" s="7" t="n">
-        <v>0.03872700106642065</v>
+        <v>0.03841931731351311</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>248438.8114155576</v>
+        <v>249798.9511949923</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>341483.7590576043</v>
+        <v>342976.4263901542</v>
       </c>
     </row>
     <row r="13">
@@ -5778,7 +5908,7 @@
         <v>0.03600000425292382</v>
       </c>
       <c r="J13" s="7" t="n">
-        <v>0.03910800426568259</v>
+        <v>0.03841931731351311</v>
       </c>
       <c r="K13" t="n">
         <v>6</v>
@@ -5787,13 +5917,13 @@
         <v>0.0387</v>
       </c>
       <c r="M13" s="7" t="n">
-        <v>0.03880200106642065</v>
+        <v>0.03841931731351311</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>243083.7098661853</v>
+        <v>244238.1083806921</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>337866.4614273199</v>
+        <v>339155.8627169397</v>
       </c>
     </row>
     <row r="14">
@@ -5827,7 +5957,7 @@
         <v>0.03600000425292382</v>
       </c>
       <c r="J14" s="7" t="n">
-        <v>0.03910800426568259</v>
+        <v>0.03841931731351311</v>
       </c>
       <c r="K14" t="n">
         <v>6</v>
@@ -5836,13 +5966,13 @@
         <v>0.0383</v>
       </c>
       <c r="M14" s="7" t="n">
-        <v>0.03850200106642065</v>
+        <v>0.03832982932837828</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>240422.7043640232</v>
+        <v>242120.6808843394</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>335720.4576150981</v>
+        <v>337554.1704475495</v>
       </c>
     </row>
     <row r="15">
@@ -5876,7 +6006,7 @@
         <v>0.03600000425292382</v>
       </c>
       <c r="J15" s="7" t="n">
-        <v>0.03910800426568259</v>
+        <v>0.03841931731351311</v>
       </c>
       <c r="K15" t="n">
         <v>6</v>
@@ -5885,13 +6015,13 @@
         <v>0.0385</v>
       </c>
       <c r="M15" s="7" t="n">
-        <v>0.03865200106642065</v>
+        <v>0.03841931731351311</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>241528.5074823232</v>
+        <v>243076.9326963737</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>337105.8405607343</v>
+        <v>338790.400303388</v>
       </c>
     </row>
     <row r="16">
@@ -5925,7 +6055,7 @@
         <v>0.03600000425292382</v>
       </c>
       <c r="J16" s="7" t="n">
-        <v>0.03910800426568259</v>
+        <v>0.03841931731351311</v>
       </c>
       <c r="K16" t="n">
         <v>6</v>
@@ -5934,13 +6064,13 @@
         <v>0.0385</v>
       </c>
       <c r="M16" s="7" t="n">
-        <v>0.03865200106642065</v>
+        <v>0.03841931731351311</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>241572.6027412946</v>
+        <v>243121.0907619448</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>337384.1967507838</v>
+        <v>339069.1529670311</v>
       </c>
     </row>
     <row r="17">
@@ -5974,7 +6104,7 @@
         <v>0.03600000425292382</v>
       </c>
       <c r="J17" s="7" t="n">
-        <v>0.03910800426568259</v>
+        <v>0.03841931731351311</v>
       </c>
       <c r="K17" t="n">
         <v>6</v>
@@ -5983,13 +6113,13 @@
         <v>0.0385</v>
       </c>
       <c r="M17" s="7" t="n">
-        <v>0.03865200106642065</v>
+        <v>0.03841931731351311</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>238594.268577947</v>
+        <v>240138.5144409193</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>334550.7188050938</v>
+        <v>336231.639188032</v>
       </c>
     </row>
     <row r="18">
@@ -6023,7 +6153,7 @@
         <v>0.03600000425292382</v>
       </c>
       <c r="J18" s="7" t="n">
-        <v>0.03910800426568259</v>
+        <v>0.03841931731351311</v>
       </c>
       <c r="K18" t="n">
         <v>6</v>
@@ -6032,13 +6162,13 @@
         <v>0.0389</v>
       </c>
       <c r="M18" s="7" t="n">
-        <v>0.03895200106642065</v>
+        <v>0.03841931731351311</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>155148.3598394828</v>
+        <v>155781.3238206417</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>252283.7028264144</v>
+        <v>253055.0204705425</v>
       </c>
     </row>
     <row r="19">
@@ -6072,7 +6202,7 @@
         <v>0.03600000425292382</v>
       </c>
       <c r="J19" s="7" t="n">
-        <v>0.03910800426568259</v>
+        <v>0.03841931731351311</v>
       </c>
       <c r="K19" t="n">
         <v>6</v>
@@ -6081,13 +6211,13 @@
         <v>0.0384</v>
       </c>
       <c r="M19" s="7" t="n">
-        <v>0.03857700106642065</v>
+        <v>0.03840482932837828</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>150432.4867039543</v>
+        <v>152009.6095060064</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>246896.1408390298</v>
+        <v>248610.6605913843</v>
       </c>
     </row>
     <row r="20">
@@ -6121,7 +6251,7 @@
         <v>0.03600000425292382</v>
       </c>
       <c r="J20" s="7" t="n">
-        <v>0.03910800426568259</v>
+        <v>0.03841931731351311</v>
       </c>
       <c r="K20" t="n">
         <v>6</v>
@@ -6130,13 +6260,13 @@
         <v>0.0383</v>
       </c>
       <c r="M20" s="7" t="n">
-        <v>0.03850200106642065</v>
+        <v>0.03832982932837828</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>153321.1965924506</v>
+        <v>154895.1110332006</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>250499.1494715615</v>
+        <v>252211.4782662145</v>
       </c>
     </row>
     <row r="21">
@@ -6170,7 +6300,7 @@
         <v>0.03600000425292382</v>
       </c>
       <c r="J21" s="7" t="n">
-        <v>0.03910800426568259</v>
+        <v>0.03841931731351311</v>
       </c>
       <c r="K21" t="n">
         <v>6</v>
@@ -6179,13 +6309,13 @@
         <v>0.0384</v>
       </c>
       <c r="M21" s="7" t="n">
-        <v>0.03857700106642065</v>
+        <v>0.03840482932837828</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>153792.5179926525</v>
+        <v>155374.4266185066</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>249833.5597365042</v>
+        <v>251552.2633693253</v>
       </c>
     </row>
     <row r="22">
@@ -6219,7 +6349,7 @@
         <v>0.03600000425292382</v>
       </c>
       <c r="J22" s="7" t="n">
-        <v>0.03910800426568259</v>
+        <v>0.03841931731351311</v>
       </c>
       <c r="K22" t="n">
         <v>6</v>
@@ -6228,13 +6358,13 @@
         <v>0.0385</v>
       </c>
       <c r="M22" s="7" t="n">
-        <v>0.03865200106642065</v>
+        <v>0.03841931731351311</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>145942.2515915434</v>
+        <v>147354.5295678807</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>242949.3147090908</v>
+        <v>244499.763634369</v>
       </c>
     </row>
     <row r="23">
@@ -6268,7 +6398,7 @@
         <v>0.03600000425292382</v>
       </c>
       <c r="J23" s="7" t="n">
-        <v>0.03910800426568259</v>
+        <v>0.03841931731351311</v>
       </c>
       <c r="K23" t="n">
         <v>6</v>
@@ -6277,13 +6407,13 @@
         <v>0.0385</v>
       </c>
       <c r="M23" s="7" t="n">
-        <v>0.03865200106642065</v>
+        <v>0.03841931731351311</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>149652.0344045617</v>
+        <v>151069.5963694577</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>246819.6304676017</v>
+        <v>248375.5920347831</v>
       </c>
     </row>
     <row r="24">
@@ -6317,7 +6447,7 @@
         <v>0.03600000425292382</v>
       </c>
       <c r="J24" s="7" t="n">
-        <v>0.03910800426568259</v>
+        <v>0.03841931731351311</v>
       </c>
       <c r="K24" t="n">
         <v>6</v>
@@ -6326,13 +6456,13 @@
         <v>0.0385</v>
       </c>
       <c r="M24" s="7" t="n">
-        <v>0.03865200106642065</v>
+        <v>0.03841931731351311</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>148319.051447991</v>
+        <v>149734.7147931979</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>246683.9178246537</v>
+        <v>248239.686091017</v>
       </c>
     </row>
     <row r="25">
@@ -6366,7 +6496,7 @@
         <v>0.03600000425292382</v>
       </c>
       <c r="J25" s="7" t="n">
-        <v>0.03910800426568259</v>
+        <v>0.03841931731351311</v>
       </c>
       <c r="K25" t="n">
         <v>6</v>
@@ -6375,13 +6505,13 @@
         <v>0.0386</v>
       </c>
       <c r="M25" s="7" t="n">
-        <v>0.03872700106642065</v>
+        <v>0.03841931731351311</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>149839.6053788741</v>
+        <v>151059.3064580217</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>248173.7786877208</v>
+        <v>249533.5409706896</v>
       </c>
     </row>
     <row r="26">
@@ -6415,7 +6545,7 @@
         <v>0.03600000425292382</v>
       </c>
       <c r="J26" s="7" t="n">
-        <v>0.03910800426568259</v>
+        <v>0.03841931731351311</v>
       </c>
       <c r="K26" t="n">
         <v>6</v>
@@ -6424,13 +6554,13 @@
         <v>0.0387</v>
       </c>
       <c r="M26" s="7" t="n">
-        <v>0.03880200106642065</v>
+        <v>0.03841931731351311</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>151182.1627999744</v>
+        <v>152205.6623514657</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>250232.6754834358</v>
+        <v>251397.2565488985</v>
       </c>
     </row>
     <row r="27">
@@ -6464,7 +6594,7 @@
         <v>0.03600000425292382</v>
       </c>
       <c r="J27" s="7" t="n">
-        <v>0.03910800426568259</v>
+        <v>0.03841931731351311</v>
       </c>
       <c r="K27" t="n">
         <v>6</v>
@@ -6473,13 +6603,13 @@
         <v>0.0389</v>
       </c>
       <c r="M27" s="7" t="n">
-        <v>0.03895200106642065</v>
+        <v>0.03841931731351311</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>146378.4225851776</v>
+        <v>146998.8952021653</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>245059.8953743136</v>
+        <v>245820.9238673372</v>
       </c>
     </row>
     <row r="28">
@@ -6513,7 +6643,7 @@
         <v>0.03519999850777533</v>
       </c>
       <c r="J28" s="7" t="n">
-        <v>0.03727039850479088</v>
+        <v>0.03664455749990904</v>
       </c>
       <c r="K28" t="n">
         <v>6</v>
@@ -6522,13 +6652,13 @@
         <v>0.0364</v>
       </c>
       <c r="M28" s="7" t="n">
-        <v>0.03661759962619772</v>
+        <v>0.03646113937497726</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>139416.2555037662</v>
+        <v>140831.8243449935</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>237528.3123144455</v>
+        <v>239078.1411518565</v>
       </c>
     </row>
     <row r="29">
@@ -6562,7 +6692,7 @@
         <v>0.03519999850777533</v>
       </c>
       <c r="J29" s="7" t="n">
-        <v>0.03727039850479088</v>
+        <v>0.03664455749990904</v>
       </c>
       <c r="K29" t="n">
         <v>6</v>
@@ -6571,13 +6701,13 @@
         <v>0.0364</v>
       </c>
       <c r="M29" s="7" t="n">
-        <v>0.03661759962619772</v>
+        <v>0.03646113937497726</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>141211.0855195762</v>
+        <v>142629.1104694502</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>240208.7893228781</v>
+        <v>241762.2862194922</v>
       </c>
     </row>
     <row r="30">
@@ -6611,7 +6741,7 @@
         <v>0.03519999850777533</v>
       </c>
       <c r="J30" s="7" t="n">
-        <v>0.03727039850479088</v>
+        <v>0.03664455749990904</v>
       </c>
       <c r="K30" t="n">
         <v>6</v>
@@ -6620,13 +6750,13 @@
         <v>0.0364</v>
       </c>
       <c r="M30" s="7" t="n">
-        <v>0.03661759962619772</v>
+        <v>0.03646113937497726</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>141141.4062495416</v>
+        <v>142559.3358478468</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>240452.0056210078</v>
+        <v>242005.8353433756</v>
       </c>
     </row>
     <row r="31">
@@ -6660,7 +6790,7 @@
         <v>0.03519999850777533</v>
       </c>
       <c r="J31" s="7" t="n">
-        <v>0.03727039850479088</v>
+        <v>0.03664455749990904</v>
       </c>
       <c r="K31" t="n">
         <v>6</v>
@@ -6669,13 +6799,13 @@
         <v>0.0364</v>
       </c>
       <c r="M31" s="7" t="n">
-        <v>0.03661759962619772</v>
+        <v>0.03646113937497726</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>142020.9139452199</v>
+        <v>143440.0470928513</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>241960.7055201396</v>
+        <v>243516.5998006186</v>
       </c>
     </row>
     <row r="32">
@@ -6709,7 +6839,7 @@
         <v>0.03519999850777533</v>
       </c>
       <c r="J32" s="7" t="n">
-        <v>0.03727039850479088</v>
+        <v>0.03664455749990904</v>
       </c>
       <c r="K32" t="n">
         <v>6</v>
@@ -6718,13 +6848,13 @@
         <v>0.0364</v>
       </c>
       <c r="M32" s="7" t="n">
-        <v>0.03661759962619772</v>
+        <v>0.03646113937497726</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>139077.1350143206</v>
+        <v>140492.239791119</v>
       </c>
       <c r="O32" s="3" t="n">
-        <v>237085.7912219367</v>
+        <v>238635.0144978894</v>
       </c>
     </row>
     <row r="33">
@@ -6758,7 +6888,7 @@
         <v>0.03519999850777533</v>
       </c>
       <c r="J33" s="7" t="n">
-        <v>0.03727039850479088</v>
+        <v>0.03664455749990904</v>
       </c>
       <c r="K33" t="n">
         <v>6</v>
@@ -6767,13 +6897,13 @@
         <v>0.0365</v>
       </c>
       <c r="M33" s="7" t="n">
-        <v>0.03669259962619772</v>
+        <v>0.03653613937497726</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>141620.7724138094</v>
+        <v>143046.3327237602</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>241256.9633769009</v>
+        <v>242818.8693619227</v>
       </c>
     </row>
     <row r="34">
@@ -6807,7 +6937,7 @@
         <v>0.03519999850777533</v>
       </c>
       <c r="J34" s="7" t="n">
-        <v>0.03727039850479088</v>
+        <v>0.03664455749990904</v>
       </c>
       <c r="K34" t="n">
         <v>6</v>
@@ -6816,13 +6946,13 @@
         <v>0.0365</v>
       </c>
       <c r="M34" s="7" t="n">
-        <v>0.03669259962619772</v>
+        <v>0.03653613937497726</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>141112.7375101839</v>
+        <v>142537.6026072685</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>240130.1119888939</v>
+        <v>241690.4759507641</v>
       </c>
     </row>
     <row r="35">
@@ -6856,7 +6986,7 @@
         <v>0.03519999850777533</v>
       </c>
       <c r="J35" s="7" t="n">
-        <v>0.03727039850479088</v>
+        <v>0.03664455749990904</v>
       </c>
       <c r="K35" t="n">
         <v>6</v>
@@ -6865,13 +6995,13 @@
         <v>0.0365</v>
       </c>
       <c r="M35" s="7" t="n">
-        <v>0.03669259962619772</v>
+        <v>0.03653613937497726</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>142726.3131340643</v>
+        <v>144153.386304898</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>242749.831522316</v>
+        <v>244313.7804007193</v>
       </c>
     </row>
     <row r="36">
@@ -6905,7 +7035,7 @@
         <v>0.03519999850777533</v>
       </c>
       <c r="J36" s="7" t="n">
-        <v>0.03727039850479088</v>
+        <v>0.03664455749990904</v>
       </c>
       <c r="K36" t="n">
         <v>6</v>
@@ -6914,13 +7044,13 @@
         <v>0.0366</v>
       </c>
       <c r="M36" s="7" t="n">
-        <v>0.03676759962619772</v>
+        <v>0.03661113937497726</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>177757.5092428544</v>
+        <v>179239.5093883398</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>243242.2097738287</v>
+        <v>244813.8214913183</v>
       </c>
     </row>
     <row r="38">
@@ -6942,10 +7072,10 @@
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr"/>
       <c r="N38" s="12" t="n">
-        <v>5838423.805440546</v>
+        <v>5882246.189186334</v>
       </c>
       <c r="O38" s="12" t="n">
-        <v>8799587.254957264</v>
+        <v>8847579.344325766</v>
       </c>
     </row>
   </sheetData>
